--- a/data/example/data_formatting/obs_columns_matching_examples/tissue_matching_table.xlsx
+++ b/data/example/data_formatting/obs_columns_matching_examples/tissue_matching_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,202 +448,202 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lung</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>lung</t>
+          <t>liver</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Liver</t>
+          <t>BRCA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>liver</t>
+          <t>breast</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Oral</t>
+          <t>CRC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>tongue</t>
+          <t>colon</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Thymus</t>
+          <t>LUAD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>immune system</t>
+          <t>lung</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LymphNode</t>
+          <t>PAAD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>lymph node</t>
+          <t>pancreas</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Uterus</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>uterus</t>
+          <t>nose</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Prostate</t>
+          <t>HNSC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>prostate gland</t>
+          <t>nose</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Blood</t>
+          <t>KIRC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>blood</t>
+          <t>kidney</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Spleen</t>
+          <t>STAD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>spleen</t>
+          <t>stomach</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kidney</t>
+          <t>ICC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kidney</t>
+          <t>liver</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bladder</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bladder organ</t>
+          <t>brain</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Skin</t>
+          <t>UVM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>skin of body</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ureter</t>
+          <t>PRAD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ureter</t>
+          <t>prostate gland</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SkeletalMuscle</t>
+          <t>ALM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -658,316 +658,226 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SalivaryGland</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>exocrine gland</t>
+          <t>uterus</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fat</t>
+          <t>cSCC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>adipose tissue</t>
+          <t>skin of body</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Vagina</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>reproductive system</t>
+          <t>liver</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Vasculature</t>
+          <t>SKCM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>vasculature</t>
+          <t>skin of body</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nose</t>
+          <t>OV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nose</t>
+          <t>ovary</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Breast</t>
+          <t>TGCT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>breast</t>
+          <t>testis</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tongue</t>
+          <t>BLCA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>tongue</t>
+          <t>bladder organ</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Heart</t>
+          <t>GCTB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>skeletal system</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pancreas</t>
+          <t>KIRP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>pancreas</t>
+          <t>kidney</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SmallIntestine</t>
+          <t>LYM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>small intestine</t>
+          <t>lymph node</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Eye</t>
+          <t>KICH</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>eye</t>
+          <t>kidney</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Colon</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>colon</t>
+          <t>endocrine gland</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Testis</t>
+          <t>OS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>testis</t>
+          <t>skeletal system</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BoneMarrow</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>bone marrow</t>
+          <t>esophagus</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Trachea</t>
+          <t>THCA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>respiratory system</t>
+          <t>endocrine gland</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Stomach</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>stomach</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>CommonBileDuct</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>gallbladder</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Omentum</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>omentum</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Esophagus</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>esophagus</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Rectum</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>large intestine</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Ovary</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>ovary</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
